--- a/data/extracted/inventory-receipts/REP CONTENEDOR INTERLOCK243 28.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR INTERLOCK243 28.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE784A3-ADEC-4B3A-B99A-479675BC0D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9135"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1664,7 +1677,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -1705,12 +1718,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1990,50 +2002,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L393"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2071,12 +2083,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2114,7 +2126,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -2152,7 +2164,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2190,7 +2202,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2228,7 +2240,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2266,7 +2278,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2304,7 +2316,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -2342,7 +2354,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -2380,7 +2392,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2418,7 +2430,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2456,7 +2468,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -2494,7 +2506,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -2532,7 +2544,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -2570,7 +2582,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -2608,7 +2620,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -2646,7 +2658,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -2684,7 +2696,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -2722,7 +2734,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2760,7 +2772,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2798,7 +2810,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -2836,7 +2848,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -2874,7 +2886,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -2912,7 +2924,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -2950,7 +2962,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F30" s="1" t="s">
         <v>73</v>
       </c>
@@ -2970,7 +2982,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F31" s="1" t="s">
         <v>43</v>
       </c>
@@ -2990,7 +3002,7 @@
         <v>434.70000000000016</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -3028,7 +3040,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -3066,7 +3078,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -3104,7 +3116,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -3142,7 +3154,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -3180,7 +3192,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -3218,7 +3230,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -3256,7 +3268,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -3294,7 +3306,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -3332,7 +3344,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -3370,7 +3382,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -3408,7 +3420,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -3446,7 +3458,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -3484,7 +3496,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -3522,7 +3534,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -3560,7 +3572,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -3598,7 +3610,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -3636,7 +3648,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -3674,7 +3686,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -3712,7 +3724,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -3750,7 +3762,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -3788,7 +3800,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -3826,7 +3838,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -3864,7 +3876,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -3902,7 +3914,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -3940,7 +3952,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -3978,7 +3990,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -4016,7 +4028,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -4054,7 +4066,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -4092,7 +4104,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -4130,7 +4142,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -4168,7 +4180,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -4206,7 +4218,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -4244,7 +4256,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -4282,7 +4294,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -4320,7 +4332,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -4358,7 +4370,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -4396,7 +4408,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -4434,7 +4446,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -4472,7 +4484,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -4510,7 +4522,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -4548,7 +4560,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -4586,7 +4598,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -4624,7 +4636,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -4662,7 +4674,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -4700,7 +4712,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -4738,7 +4750,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -4776,7 +4788,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -4814,7 +4826,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -4852,7 +4864,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -4890,7 +4902,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -4928,7 +4940,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -4966,7 +4978,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -5004,7 +5016,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -5042,7 +5054,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -5080,7 +5092,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -5118,7 +5130,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -5156,7 +5168,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -5194,7 +5206,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -5232,7 +5244,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -5270,7 +5282,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -5308,7 +5320,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -5346,7 +5358,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -5384,7 +5396,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -5422,7 +5434,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -5460,7 +5472,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -5498,7 +5510,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -5536,7 +5548,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -5574,7 +5586,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -5612,7 +5624,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -5650,7 +5662,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -5688,7 +5700,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -5726,7 +5738,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -5764,7 +5776,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -5802,7 +5814,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -5840,7 +5852,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -5878,7 +5890,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -5916,7 +5928,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -5954,7 +5966,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -5992,7 +6004,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -6030,7 +6042,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -6068,7 +6080,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F113" s="1" t="s">
         <v>73</v>
       </c>
@@ -6088,7 +6100,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F114" s="1" t="s">
         <v>213</v>
       </c>
@@ -6111,7 +6123,7 @@
         <v>1549.1999999999987</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -6149,7 +6161,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -6187,7 +6199,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -6225,7 +6237,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -6263,7 +6275,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -6301,7 +6313,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -6339,7 +6351,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -6377,7 +6389,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -6415,7 +6427,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -6453,7 +6465,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -6491,7 +6503,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -6529,7 +6541,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -6567,7 +6579,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -6605,7 +6617,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -6643,7 +6655,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -6681,7 +6693,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -6719,7 +6731,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -6757,7 +6769,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -6795,7 +6807,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -6833,7 +6845,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -6871,7 +6883,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -6909,7 +6921,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -6947,7 +6959,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -6985,7 +6997,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -7023,7 +7035,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -7061,7 +7073,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F140" s="1" t="s">
         <v>73</v>
       </c>
@@ -7081,7 +7093,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F141" s="1" t="s">
         <v>45</v>
       </c>
@@ -7104,7 +7116,7 @@
         <v>399.00000000000006</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -7142,7 +7154,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -7180,7 +7192,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -7218,7 +7230,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -7256,7 +7268,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -7294,7 +7306,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -7332,7 +7344,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -7370,7 +7382,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -7408,7 +7420,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -7446,7 +7458,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -7484,7 +7496,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -7522,7 +7534,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -7560,7 +7572,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -7598,7 +7610,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -7636,7 +7648,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -7674,7 +7686,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -7712,7 +7724,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -7750,7 +7762,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -7788,7 +7800,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -7826,7 +7838,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -7864,7 +7876,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -7902,7 +7914,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -7940,7 +7952,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -7978,7 +7990,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -8016,7 +8028,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -8054,7 +8066,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -8092,7 +8104,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -8130,7 +8142,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -8168,7 +8180,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -8206,7 +8218,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -8244,7 +8256,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -8282,7 +8294,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -8320,7 +8332,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -8358,7 +8370,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -8396,7 +8408,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -8434,7 +8446,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -8472,7 +8484,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -8510,7 +8522,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -8548,7 +8560,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -8586,7 +8598,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -8624,7 +8636,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -8662,7 +8674,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -8700,7 +8712,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -8738,7 +8750,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -8776,7 +8788,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -8814,7 +8826,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -8852,7 +8864,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -8890,7 +8902,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -8928,7 +8940,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -8966,7 +8978,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -9004,7 +9016,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -9042,7 +9054,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -9080,7 +9092,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -9118,7 +9130,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -9156,7 +9168,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -9194,7 +9206,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -9232,7 +9244,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -9270,7 +9282,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -9308,7 +9320,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -9346,7 +9358,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -9384,7 +9396,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -9422,7 +9434,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -9460,7 +9472,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -9498,7 +9510,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -9536,7 +9548,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -9574,7 +9586,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -9612,7 +9624,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -9650,7 +9662,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -9688,7 +9700,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -9726,7 +9738,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -9764,7 +9776,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -9802,7 +9814,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -9840,7 +9852,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -9878,7 +9890,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -9916,7 +9928,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -9954,7 +9966,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -9992,7 +10004,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -10030,7 +10042,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -10068,7 +10080,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -10106,7 +10118,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -10144,7 +10156,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -10182,7 +10194,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -10220,7 +10232,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -10258,7 +10270,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -10296,7 +10308,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -10334,7 +10346,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -10372,7 +10384,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -10410,7 +10422,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -10448,7 +10460,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -10486,7 +10498,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -10524,7 +10536,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -10562,7 +10574,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -10600,7 +10612,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -10638,7 +10650,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -10676,7 +10688,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -10714,7 +10726,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -10752,7 +10764,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -10790,7 +10802,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
         <v>19</v>
       </c>
@@ -10828,7 +10840,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
         <v>19</v>
       </c>
@@ -10866,7 +10878,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -10904,7 +10916,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -10942,7 +10954,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -10980,7 +10992,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -11018,7 +11030,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -11056,7 +11068,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -11094,7 +11106,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -11132,7 +11144,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -11170,7 +11182,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -11208,7 +11220,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -11246,7 +11258,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -11284,7 +11296,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -11322,7 +11334,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -11360,7 +11372,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -11398,7 +11410,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -11436,7 +11448,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -11474,7 +11486,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -11512,7 +11524,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -11550,7 +11562,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -11588,7 +11600,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -11626,7 +11638,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -11664,7 +11676,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -11702,7 +11714,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -11740,7 +11752,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -11778,7 +11790,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -11816,7 +11828,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -11854,7 +11866,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -11892,7 +11904,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -11930,7 +11942,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -11968,7 +11980,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -12006,7 +12018,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -12044,7 +12056,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -12082,7 +12094,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -12120,7 +12132,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -12158,7 +12170,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -12196,7 +12208,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -12234,7 +12246,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -12272,7 +12284,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -12310,7 +12322,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -12348,7 +12360,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F280" s="1" t="s">
         <v>73</v>
       </c>
@@ -12368,7 +12380,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F281" s="1" t="s">
         <v>439</v>
       </c>
@@ -12388,7 +12400,7 @@
         <v>2683.2999999999934</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -12426,7 +12438,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -12464,7 +12476,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -12502,7 +12514,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -12540,7 +12552,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -12578,7 +12590,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -12616,7 +12628,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -12654,7 +12666,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -12692,7 +12704,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -12730,7 +12742,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -12768,7 +12780,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -12806,7 +12818,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -12844,7 +12856,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -12882,7 +12894,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -12920,7 +12932,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -12958,7 +12970,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -12996,7 +13008,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -13034,7 +13046,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -13072,7 +13084,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -13110,7 +13122,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -13148,7 +13160,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -13186,7 +13198,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -13224,7 +13236,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -13262,7 +13274,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -13300,7 +13312,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -13338,7 +13350,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -13376,7 +13388,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -13414,7 +13426,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -13452,7 +13464,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
         <v>19</v>
       </c>
@@ -13490,7 +13502,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -13528,7 +13540,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -13566,7 +13578,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -13604,7 +13616,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -13642,7 +13654,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -13680,7 +13692,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -13718,7 +13730,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -13756,7 +13768,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -13794,7 +13806,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F319" s="1" t="s">
         <v>73</v>
       </c>
@@ -13814,7 +13826,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F320" s="1" t="s">
         <v>481</v>
       </c>
@@ -13834,7 +13846,7 @@
         <v>726.7</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -13872,7 +13884,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -13910,7 +13922,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -13948,7 +13960,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -13986,7 +13998,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -14024,7 +14036,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -14062,7 +14074,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -14100,7 +14112,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -14138,7 +14150,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -14176,7 +14188,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -14214,7 +14226,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -14252,7 +14264,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -14290,7 +14302,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -14328,7 +14340,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -14366,7 +14378,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -14404,7 +14416,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -14442,7 +14454,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -14480,7 +14492,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -14518,7 +14530,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -14556,7 +14568,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -14594,7 +14606,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -14632,7 +14644,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -14670,7 +14682,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -14708,7 +14720,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F344" s="1" t="s">
         <v>73</v>
       </c>
@@ -14728,7 +14740,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F345" s="1" t="s">
         <v>508</v>
       </c>
@@ -14748,7 +14760,7 @@
         <v>443.3</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -14786,7 +14798,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -14824,7 +14836,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -14862,7 +14874,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -14900,7 +14912,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -14938,7 +14950,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -14976,7 +14988,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -15014,7 +15026,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -15052,7 +15064,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -15090,7 +15102,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -15128,7 +15140,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -15166,7 +15178,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -15204,7 +15216,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -15242,7 +15254,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -15280,7 +15292,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -15318,7 +15330,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -15356,7 +15368,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -15394,7 +15406,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -15432,7 +15444,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -15470,7 +15482,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -15508,7 +15520,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -15546,7 +15558,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -15584,7 +15596,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -15622,7 +15634,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F369" s="1" t="s">
         <v>73</v>
       </c>
@@ -15642,7 +15654,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F370" s="1" t="s">
         <v>508</v>
       </c>
@@ -15662,7 +15674,7 @@
         <v>435.7</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F371" s="1" t="s">
         <v>73</v>
       </c>
@@ -15682,12 +15694,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J372" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>535</v>
       </c>
@@ -15725,7 +15737,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F374" s="1" t="s">
         <v>73</v>
       </c>
@@ -15745,7 +15757,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>535</v>
       </c>
@@ -15783,7 +15795,7 @@
         <v>95.7</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F377" s="1" t="s">
         <v>73</v>
       </c>
@@ -15803,12 +15815,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K378" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>535</v>
       </c>
@@ -15846,7 +15858,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F380" s="1" t="s">
         <v>73</v>
       </c>
@@ -15866,7 +15878,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J381" s="2" t="s">
         <v>24</v>
       </c>
@@ -15874,7 +15886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>535</v>
       </c>
@@ -15912,7 +15924,7 @@
         <v>167.1</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F383" s="1" t="s">
         <v>73</v>
       </c>
@@ -15932,7 +15944,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>535</v>
       </c>
@@ -15970,7 +15982,7 @@
         <v>46.3</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F386" s="1" t="s">
         <v>73</v>
       </c>
@@ -15990,7 +16002,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J387" s="2" t="s">
         <v>24</v>
       </c>
@@ -15998,7 +16010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>535</v>
       </c>
@@ -16036,7 +16048,7 @@
         <v>28.1</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F389" s="1" t="s">
         <v>73</v>
       </c>
@@ -16056,7 +16068,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J390" s="2" t="s">
         <v>24</v>
       </c>
@@ -16064,7 +16076,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>535</v>
       </c>
@@ -16102,7 +16114,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F392" s="1" t="s">
         <v>73</v>
       </c>
@@ -16122,7 +16134,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="J393" s="2" t="s">
         <v>24</v>
       </c>
@@ -16134,4 +16146,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E099FC-A0FB-4E08-AF99-9D0B2AAE4C2F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47502</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>